--- a/results/385_1/clone_summary.xlsx
+++ b/results/385_1/clone_summary.xlsx
@@ -489,7 +489,7 @@
         </is>
       </c>
       <c r="H2" t="n">
-        <v>71</v>
+        <v>66</v>
       </c>
     </row>
   </sheetData>
